--- a/results/Int All Data -0.1/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_7_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8311243860810199</v>
+        <v>0.8222114684460987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8181074791545375</v>
+        <v>0.8198951216558936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.777817309654016</v>
+        <v>0.8186243653475184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.771900175654225</v>
+        <v>0.8164626904786785</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7722310823385399</v>
+        <v>0.8176981998344637</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7662963248624539</v>
+        <v>0.8183247662505038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7644166256143337</v>
+        <v>0.8175924589766939</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7631282458296635</v>
+        <v>0.807726007606707</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7631634927822535</v>
+        <v>0.8080569142910221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7644871195195135</v>
+        <v>0.8147416025172129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7646104838535783</v>
+        <v>0.8091025047728519</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.769084566147334</v>
+        <v>0.8094157879808721</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.769084566147334</v>
+        <v>0.8210953840590889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7625408657315028</v>
+        <v>0.8120101710265073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7582567023117025</v>
+        <v>0.8120101710265073</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7582567023117025</v>
+        <v>0.8079374893222466</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7550357528500271</v>
+        <v>0.8079374893222466</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7467846485837359</v>
+        <v>0.8073990402876814</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7840576789425582</v>
+        <v>0.8070505101270715</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7824207689972781</v>
+        <v>0.8066667330138715</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7801749161122529</v>
+        <v>0.7892422983335241</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7776999580353929</v>
+        <v>0.7936106397695097</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7792663740754932</v>
+        <v>0.8031990548840666</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7809561544496582</v>
+        <v>0.8006927892199062</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7806781181942282</v>
+        <v>0.8025901119443215</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7825049470134635</v>
+        <v>0.8032343018366566</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7872962518805287</v>
+        <v>0.7972290504553907</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7875566646596637</v>
+        <v>0.7975247101871157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7853636822035234</v>
+        <v>0.7745277323022978</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7861977909698137</v>
+        <v>0.7783752481800132</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7781326662121884</v>
+        <v>0.7786885313880333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.775555906642848</v>
+        <v>0.7780619649719932</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.775555906642848</v>
+        <v>0.7753481569575826</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7976914075393646</v>
+        <v>0.7766012897896628</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7968396752967793</v>
+        <v>0.7766894071711377</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7978147718734294</v>
+        <v>0.7766894071711377</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7957451537513539</v>
+        <v>0.7839654148607786</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7941611142349587</v>
+        <v>0.7926531666691548</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7938302075506436</v>
+        <v>0.7920266002531147</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7942316081401386</v>
+        <v>0.7926531666691548</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7976777234283592</v>
+        <v>0.7926531666691548</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7997473415504346</v>
+        <v>0.8123900087744178</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7978500188260194</v>
+        <v>0.8147416025172129</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7982514194155144</v>
+        <v>0.8147416025172129</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7976424764757692</v>
+        <v>0.815403415885843</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8012824500032345</v>
+        <v>0.8151253796304129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8011767091454647</v>
+        <v>0.8151253796304129</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8041548693042998</v>
+        <v>0.8154562863147279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8019266398955696</v>
+        <v>0.8267344818034497</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8052141438971353</v>
+        <v>0.8257417617505047</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8058583337894704</v>
+        <v>0.8238581231370949</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7922735362562594</v>
+        <v>0.8268010363433402</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7917527106979891</v>
+        <v>0.8318703774658354</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.791143767758244</v>
+        <v>0.8255928952095659</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7930410904826592</v>
+        <v>0.8188553365544902</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.798176986145045</v>
+        <v>0.8236563861672712</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7919465689372338</v>
+        <v>0.8248077175068711</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7840792417841427</v>
+        <v>0.8215867680451957</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7761766676784616</v>
+        <v>0.8255047778280911</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7687949191310506</v>
+        <v>0.8245649282040309</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7686226237333904</v>
+        <v>0.8111190451310275</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7658206983375049</v>
+        <v>0.8222288845873784</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7638176347553198</v>
+        <v>0.8215670712187484</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7575735334365032</v>
+        <v>0.8103691143809225</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7568940965915782</v>
+        <v>0.8088203218171173</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7595413500660984</v>
+        <v>0.8024489167989464</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6846706027145959</v>
+        <v>0.7925648419526645</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6840264128222608</v>
+        <v>0.7957681679380451</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.682178021161441</v>
+        <v>0.8083602454183108</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6713501573258096</v>
+        <v>0.7946265813441612</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6760141584935204</v>
+        <v>0.7943427397083045</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6769716315938755</v>
+        <v>0.7962576859090147</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6755285798878401</v>
+        <v>0.8041641993799854</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6733453421774157</v>
+        <v>0.7875033795607483</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6661495731386706</v>
+        <v>0.7853006523588919</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.655811227274009</v>
+        <v>0.7862091943956516</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6578789793809474</v>
+        <v>0.7801568779659274</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6429334421427493</v>
+        <v>0.7795303115498873</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6244634169805718</v>
+        <v>0.7799630197266827</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6091830336927693</v>
+        <v>0.7867182018580534</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6088697504847493</v>
+        <v>0.7950966098236989</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.596532280403192</v>
+        <v>0.7891892205696239</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5624901515867764</v>
+        <v>0.7884001035016396</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5805587761594588</v>
+        <v>0.7782809107480813</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5833646409206338</v>
+        <v>0.7800235615511313</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5833646409206338</v>
+        <v>0.7847267490367216</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5718260326527769</v>
+        <v>0.740363690496924</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5643072356602957</v>
+        <v>0.775684661687309</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5608434968957802</v>
+        <v>0.775684661687309</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5598684003191301</v>
+        <v>0.775702285163604</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5652783928716563</v>
+        <v>0.7738578328680736</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5713541381581021</v>
+        <v>0.7278110066695528</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5732475215172279</v>
+        <v>0.715138690538391</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.589945454304192</v>
+        <v>0.6951569857801353</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5741931765217146</v>
+        <v>0.6954878924644503</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5735313631530845</v>
+        <v>0.6868393269739538</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.579103906357555</v>
+        <v>0.6401207353260716</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.570799931662379</v>
+        <v>0.6391182705274105</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5525277041047357</v>
+        <v>0.6391182705274105</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5133673031022294</v>
+        <v>0.6177895101751731</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5102873414509138</v>
+        <v>0.6177895101751731</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5159264391952748</v>
+        <v>0.6239005024142089</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5093964228904492</v>
+        <v>0.6208891686529361</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5093964228904492</v>
+        <v>0.608651634048722</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5118987491893201</v>
+        <v>0.6119567615265828</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5118987491893201</v>
+        <v>0.6061277449082667</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5055528463780231</v>
+        <v>0.5850672760657434</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5055880933306132</v>
+        <v>0.5630611522187334</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5055880933306132</v>
+        <v>0.5492393707631089</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5055880933306132</v>
+        <v>0.5398251170613496</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5055880933306132</v>
+        <v>0.5216134313281549</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5125195102249336</v>
+        <v>0.5215566215339805</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5093338077158482</v>
+        <v>0.5245032667705001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5006578740033406</v>
+        <v>0.488237262580674</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4977678312259802</v>
+        <v>0.4884800518835142</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4932408785033398</v>
+        <v>0.4572278230321004</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4939026918719698</v>
+        <v>0.4834536291091727</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4945116348117149</v>
+        <v>0.4887873223760925</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4955396018172499</v>
+        <v>0.5359114613137741</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4955396018172499</v>
+        <v>0.5268067587897607</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4966028157753749</v>
+        <v>0.5454511526997506</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4969337224596899</v>
+        <v>0.5266423421226794</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4969337224596899</v>
+        <v>0.5410846772789021</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4969337224596899</v>
+        <v>0.5395358847150968</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.49759553582832</v>
+        <v>0.5301550119507903</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.49829259614954</v>
+        <v>0.5203551151206939</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.499285316202485</v>
+        <v>0.5200418319126738</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4995985994105051</v>
+        <v>0.519507322243398</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4986058793575601</v>
+        <v>0.531090922209561</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4995985994105051</v>
+        <v>0.4598754911766511</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5002780362554301</v>
+        <v>0.4701609666124278</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5002780362554301</v>
+        <v>0.4531574220130073</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5005913194634501</v>
+        <v>0.4436552582647884</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4992324457736002</v>
+        <v>0.5170696844692804</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4928747248664347</v>
+        <v>0.5155385153817701</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4932056315507498</v>
+        <v>0.5280874671788671</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.49623666213847</v>
+        <v>0.5252405500846756</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.49623666213847</v>
+        <v>0.5323245655502091</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4836093377056141</v>
+        <v>0.531608015737557</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4836093377056141</v>
+        <v>0.531608015737557</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4992676927261901</v>
+        <v>0.5108687088336328</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4989896564707599</v>
+        <v>0.496667296965113</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.5158814474969687</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.50031328320802</v>
+        <v>0.5158814474969687</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5033364350651612</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5092888160175422</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5067257405592074</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5068177973059718</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.5026609375855257</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.5026609375855257</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.5002427893028402</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.499669093315685</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.499669093315685</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.50031328320802</v>
+        <v>0.499669093315685</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.50031328320802</v>
+        <v>0.499669093315685</v>
       </c>
     </row>
   </sheetData>
